--- a/public/templates/Informatika_9-sinf_savollar_banki.xlsx
+++ b/public/templates/Informatika_9-sinf_savollar_banki.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Savollar" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yoʻriqnoma" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Savollar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Yoʻriqnoma" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Savollar'!$A$1:$Q$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Savollar'!$A$1:$Q$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -206,7 +206,7 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Roʻyxatdan tanlang: Test, Toʻgʻri/Notoʻgʻri, Rasmli, Qisqa javob, Mantiqiy.</t>
+        <t>Roʻyxatdan tanlang: Test, Toʻgʻri/Notoʻgʻri, Rasmli, Qisqa javob, Mantiqiy, Moslashtirish, Koʻp bosqichli.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
@@ -216,14 +216,18 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Test, Rasmli va Mantiqiy savollar uchun variantlar. Kamida A va B toʻldirilsin.</t>
+        <t>Test, Rasmli va Mantiqiy savollar uchun variantlar. Kamida A va B toʻldirilsin.
+Moslashtirish: har bir katakda juftlik “Chap = Oʻng” (masalan: Klaviatura = Kiritish).
+Koʻp bosqichli: har bir katak — bitta qadam “Qadam matni || variant | variant | variant”.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Test/Rasmli/Mantiqiy: A, B, C yoki D.
 Toʻgʻri/Notoʻgʻri: Toʻgʻri yoki Notoʻgʻri.
-Qisqa javob: javob(lar), bir nechta boʻlsa ; bilan ajrating (masalan: 6; olti).</t>
+Qisqa javob: javob(lar), bir nechta boʻlsa ; bilan ajrating (masalan: 6; olti).
+Moslashtirish: boʻsh qoldiring (juftliklar variantlarda).
+Koʻp bosqichli: har bir qadam uchun harf, vergul bilan (masalan: A, C, B).</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
@@ -559,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q118"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5749,67 +5753,63 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Rasmli</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Rasmdagi kompyuter qismi qaysi?</t>
+          <t>1 bayt necha bitdan iborat?</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Quvvat bloki</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Markaziy protsessor (CPU)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Qattiq disk (HDD)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Operativ xotira (RAM)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>RAM moduli — mikrosxemalar oʻrnatilgan uzun plata; u ishlayotgan dasturlarni vaqtincha saqlaydi.</t>
+          <t>1 bayt = 8 bit. Bit — eng kichik maʼlumot birligi (0 yoki 1).</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>U ona plataga uzun uyachaga oʻrnatiladi.</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>/assets/devices/ram.webp</t>
-        </is>
-      </c>
+          <t>Bu son 2 ning kubiga teng.</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>oʻrta</t>
+          <t>oson</t>
         </is>
       </c>
       <c r="O69" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -5823,72 +5823,68 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter tizimining asosiy komponentlari</t>
+          <t>Chiqarish qurilmalari</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Rasmli</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Rasmdagi qism qaysi?</t>
+          <t>Qaysi biri chiqarish qurilmasi?</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Operativ xotira (RAM)</t>
+          <t>Karnay</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Tarmoq adapteri</t>
+          <t>Sichqoncha</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Markaziy protsessor (CPU)</t>
+          <t>Mikrofon</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>Skaner</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Protsessor — kvadrat shakldagi mikrosxema; u dastur buyruqlarini bajaradi.</t>
+          <t>Karnay ovozni chiqaradi.</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Bu kompyuterning “miyasi”.</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>/assets/devices/cpu.webp</t>
-        </is>
-      </c>
+          <t>Undan musiqa eshitiladi.</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>oʻrta</t>
+          <t>oson</t>
         </is>
       </c>
       <c r="O70" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71">
@@ -5902,72 +5898,68 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Chiqarish qurilmalari</t>
+          <t>Kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Rasmli</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Rasmdagi qurilma nima yasaydi?</t>
+          <t>Klaviatura qanday qurilma?</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Ovozli fayllarni</t>
+          <t>Kiritish qurilmasi</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Qogʻoz hujjatlarni</t>
+          <t>Saqlash qurilmasi</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Uch oʻlchamli (3D) obyektlarni</t>
+          <t>Chiqarish qurilmasi</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Fotosuratlarni</t>
+          <t>Protsessor</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>3D printer raqamli modeldan plastikni qatlamma-qatlam eritib qoʻyib, haqiqiy buyum yasaydi.</t>
+          <t>Klaviatura orqali matn va buyruqlar kiritiladi.</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Natija — qoʻlda ushlasa boʻladigan buyum.</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>/assets/devices/printer_3d.webp</t>
-        </is>
-      </c>
+          <t>Biz unda yozamiz.</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>oson</t>
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="Q71" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -5981,72 +5973,68 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
+          <t>Kompyuter tizimining asosiy komponentlari</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Rasmli</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Rasmdagi qurilma qayerda ishlatiladi?</t>
+          <t>CPU qisqartmasi nimani bildiradi?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Hujjat chop etishda</t>
+          <t>Kompyuter quvvat bloki</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Rasm chizishda</t>
+          <t>Rangli ekran</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Ovoz yozishda</t>
+          <t>Markaziy protsessor</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Doʻkonda bank kartasi bilan toʻlov qilishda</t>
+          <t>Markaziy printer</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Toʻlov terminali karta chipini (chip va PIN) yoki kontaktsiz (NFC) maʼlumotni oʻqiydi.</t>
+          <t>CPU — Central Processing Unit, yaʼni markaziy protsessor.</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Unda PIN-kod teriladi.</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>/assets/devices/pos_terminal.webp</t>
-        </is>
-      </c>
+          <t>C — Central.</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>oʻrta</t>
+          <t>oson</t>
         </is>
       </c>
       <c r="O72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="Q72" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -6060,72 +6048,52 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Yangi texnologiyalarning taʼsiri</t>
+          <t>Kompyuter tizimining asosiy komponentlari</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Rasmli</t>
+          <t>Toʻgʻri/Notoʻgʻri</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Rasmdagi qurilma qaysi texnologiyaga tegishli?</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Virtual reallik (VR)</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Shtrix-kod</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Bulutli saqlash</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>Lazerli chop etish</t>
-        </is>
-      </c>
+          <t>RAM — elektr oʻchganda ham maʼlumotni saqlaydigan doimiy xotira.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Notoʻgʻri</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>VR koʻzoynak foydalanuvchini toʻliq virtual muhitga olib kiradi: taʼlim, tibbiyot va oʻyinlarda qoʻllanadi.</t>
+          <t>Notoʻgʻri. RAM energiyaga bogʻliq xotira: elektr oʻchsa, maʼlumot yoʻqoladi.</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>U koʻzga taqiladi va boshqa dunyoni koʻrsatadi.</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>/assets/devices/vr_headset.webp</t>
-        </is>
-      </c>
+          <t>Saqlanmagan hujjat nima boʻladi?</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>oson</t>
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -6139,37 +6107,37 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Yangi texnologiyalarning taʼsiri</t>
+          <t>Operatsion tizimlar</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Rasmli</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Rasmdagi uchuvchi qurilma qanday ataladi?</t>
+          <t>Qaysi biri operatsion tizim EMAS?</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Proyektor</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Sunʼiy yoʻldosh</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Dron (uchuvchisiz uchish apparati)</t>
+          <t>Microsoft Excel</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Vertolyot modeli</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -6179,32 +6147,28 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Dronlar kamera va sensorlar bilan jihozlanadi: xaritalash, yetkazib berish, qishloq xoʻjaligida qoʻllanadi.</t>
+          <t>Excel — elektron jadval dasturi (amaliy dastur). Qolganlari operatsion tizimlar.</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Unda bir nechta parrak bor va u masofadan boshqariladi.</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>/assets/devices/drone.webp</t>
-        </is>
-      </c>
+          <t>Bu dasturda jadvallar tuziladi.</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>oson</t>
         </is>
       </c>
       <c r="O74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
@@ -6218,7 +6182,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter tizimining asosiy komponentlari</t>
+          <t>Operatsion tizimlar</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6228,27 +6192,27 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1 bayt necha bitdan iborat?</t>
+          <t>Android qaysi qurilmalar uchun mashhur operatsion tizim?</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Fleshkalar</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Smartfon va planshetlar</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Printerlar</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Faqat superkompyuterlar</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -6258,12 +6222,12 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>1 bayt = 8 bit. Bit — eng kichik maʼlumot birligi (0 yoki 1).</t>
+          <t>Android — mobil qurilmalar uchun eng keng tarqalgan operatsion tizimlardan biri.</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Bu son 2 ning kubiga teng.</t>
+          <t>Choʻntagingizdagi qurilmani eslang.</t>
         </is>
       </c>
       <c r="M75" s="2" t="n"/>
@@ -6293,7 +6257,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Chiqarish qurilmalari</t>
+          <t>Saqlash qurilmalari va maʼlumot almashish</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6303,27 +6267,27 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Qaysi biri chiqarish qurilmasi?</t>
+          <t>DVD qanday saqlash vositasi?</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Karnay</t>
+          <t>Optik</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Sichqoncha</t>
+          <t>Magnit</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Mikrofon</t>
+          <t>Bulutli</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Skaner</t>
+          <t>Flesh</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -6333,12 +6297,12 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Karnay ovozni chiqaradi.</t>
+          <t>DVD lazer nuri bilan oʻqiladi — u optik vosita.</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Undan musiqa eshitiladi.</t>
+          <t>Lazer!</t>
         </is>
       </c>
       <c r="M76" s="2" t="n"/>
@@ -6368,7 +6332,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Kiritish qurilmalari</t>
+          <t>Chiqarish qurilmalari</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -6378,27 +6342,27 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Klaviatura qanday qurilma?</t>
+          <t>Qaysi qurilma hujjatni qogʻozga chiqaradi?</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Kiritish qurilmasi</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Saqlash qurilmasi</t>
+          <t>Skaner</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Chiqarish qurilmasi</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Protsessor</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -6408,12 +6372,12 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Klaviatura orqali matn va buyruqlar kiritiladi.</t>
+          <t>Printer — qogʻozga chop etuvchi chiqarish qurilmasi.</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Biz unda yozamiz.</t>
+          <t>Chop etish.</t>
         </is>
       </c>
       <c r="M77" s="2" t="n"/>
@@ -6443,52 +6407,36 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter tizimining asosiy komponentlari</t>
+          <t>Kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Toʻgʻri/Notoʻgʻri</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>CPU qisqartmasi nimani bildiradi?</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Kompyuter quvvat bloki</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Rangli ekran</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Markaziy protsessor</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Markaziy printer</t>
-        </is>
-      </c>
+          <t>Skaner — chiqarish qurilmasi.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Notoʻgʻri</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>CPU — Central Processing Unit, yaʼni markaziy protsessor.</t>
+          <t>Notoʻgʻri. Skaner qogʻozdagi maʼlumotni kompyuterga KIRITADI.</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>C — Central.</t>
+          <t>Maʼlumot qaysi tomonga harakatlanadi?</t>
         </is>
       </c>
       <c r="M78" s="2" t="n"/>
@@ -6523,37 +6471,53 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Toʻgʻri/Notoʻgʻri</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>RAM — elektr oʻchganda ham maʼlumotni saqlaydigan doimiy xotira.</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
+          <t>Maktab informatika kursida 1 KB necha baytga teng deb olinadi?</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Notoʻgʻri</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Notoʻgʻri. RAM energiyaga bogʻliq xotira: elektr oʻchsa, maʼlumot yoʻqoladi.</t>
+          <t>1 KB = 1024 bayt (2¹⁰). Xalqaro SI tizimida 1 kB = 1000 bayt deb ham yoziladi.</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Saqlanmagan hujjat nima boʻladi?</t>
+          <t>Bu 2 ning 10-darajasi.</t>
         </is>
       </c>
       <c r="M79" s="2" t="n"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>oson</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O79" s="2" t="n">
@@ -6577,7 +6541,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Operatsion tizimlar</t>
+          <t>Kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -6587,42 +6551,42 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Qaysi biri operatsion tizim EMAS?</t>
+          <t>Qaysi qurilma ovozni kompyuterga kiritadi?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Mikrofon</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Windows</t>
+          <t>Karnay</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Microsoft Excel</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Excel — elektron jadval dasturi (amaliy dastur). Qolganlari operatsion tizimlar.</t>
+          <t>Mikrofon — ovozli kiritish qurilmasi.</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Bu dasturda jadvallar tuziladi.</t>
+          <t>Unga gapiriladi.</t>
         </is>
       </c>
       <c r="M80" s="2" t="n"/>
@@ -6652,7 +6616,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Operatsion tizimlar</t>
+          <t>Kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -6662,48 +6626,48 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Android qaysi qurilmalar uchun mashhur operatsion tizim?</t>
+          <t>Smartfon ekrani telefon burilganda ham aylanishi uchun qaysi sensor ishlaydi?</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Fleshkalar</t>
+          <t>Barmoq izi skaneri</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Smartfon va planshetlar</t>
+          <t>Termometr</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Printerlar</t>
+          <t>Akselerometr</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Faqat superkompyuterlar</t>
+          <t>Mikrofon</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Android — mobil qurilmalar uchun eng keng tarqalgan operatsion tizimlardan biri.</t>
+          <t>Akselerometr qurilmaning holati va harakatini aniqlaydi.</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Choʻntagingizdagi qurilmani eslang.</t>
+          <t>U tezlanishni oʻlchaydi.</t>
         </is>
       </c>
       <c r="M81" s="2" t="n"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>oson</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O81" s="2" t="n">
@@ -6737,27 +6701,27 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>DVD qanday saqlash vositasi?</t>
+          <t>USB fleshka qanday xotira turiga asoslangan?</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Optik</t>
+          <t>Flesh-xotira (qattiq jismli)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Magnit</t>
+          <t>Magnit disk</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Bulutli</t>
+          <t>Optik disk</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Flesh</t>
+          <t>Magnit lenta</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -6767,12 +6731,12 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>DVD lazer nuri bilan oʻqiladi — u optik vosita.</t>
+          <t>Fleshka — flesh-xotira mikrosxemasiga ega qattiq jismli qurilma.</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Lazer!</t>
+          <t>Nomi oʻzida.</t>
         </is>
       </c>
       <c r="M82" s="2" t="n"/>
@@ -6802,7 +6766,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Chiqarish qurilmalari</t>
+          <t>Saqlash qurilmalari va maʼlumot almashish</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -6812,27 +6776,27 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Qaysi qurilma hujjatni qogʻozga chiqaradi?</t>
+          <t>Bluetooth nima uchun ishlatiladi?</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Qurilmalar orasida qisqa masofada simsiz maʼlumot almashish uchun</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Skaner</t>
+          <t>Uzoq masofaga elektr energiyasini uzatish uchun</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Maʼlumotni magnit lentaga yozish uchun</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Hujjatlarni chop etish uchun</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -6842,18 +6806,18 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Printer — qogʻozga chop etuvchi chiqarish qurilmasi.</t>
+          <t>Bluetooth — qisqa masofali (odatda 10 m atrofida) simsiz aloqa texnologiyasi.</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Chop etish.</t>
+          <t>Simsiz quloqchinlar shu orqali ulanadi.</t>
         </is>
       </c>
       <c r="M83" s="2" t="n"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>oson</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O83" s="2" t="n">
@@ -6877,36 +6841,52 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Kiritish qurilmalari</t>
+          <t>Kompyuter turlari</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Toʻgʻri/Notoʻgʻri</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Skaner — chiqarish qurilmasi.</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
+          <t>Qaysi qurilma eng koʻchma (mobil) hisoblanadi?</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Server shkafi</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Smartfon</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Mainframe</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Stol kompyuteri</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Notoʻgʻri</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Notoʻgʻri. Skaner qogʻozdagi maʼlumotni kompyuterga KIRITADI.</t>
+          <t>Smartfon choʻntakka sigʻadi va doimiy internetga ulanishi mumkin.</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Maʼlumot qaysi tomonga harakatlanadi?</t>
+          <t>U choʻntakka sigʻadi.</t>
         </is>
       </c>
       <c r="M84" s="2" t="n"/>
@@ -6941,47 +6921,47 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Mantiqiy</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Maktab informatika kursida 1 KB necha baytga teng deb olinadi?</t>
+          <t>Ketma-ketlikni davom ettiring: 1, 2, 4, 8, 16, ?</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>1 KB = 1024 bayt (2¹⁰). Xalqaro SI tizimida 1 kB = 1000 bayt deb ham yoziladi.</t>
+          <t>Har bir son oldingisidan 2 marta katta. Bu ikkilik sanoq tizimidagi razryad qiymatlari: 2⁰, 2¹, 2², …</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Bu 2 ning 10-darajasi.</t>
+          <t>Har safar ikkiga koʻpaytiring.</t>
         </is>
       </c>
       <c r="M85" s="2" t="n"/>
@@ -6991,13 +6971,13 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P85" s="2" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
@@ -7011,68 +6991,52 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Kiritish qurilmalari</t>
+          <t>Kompyuter tizimining asosiy komponentlari</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Qisqa javob</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Qaysi qurilma ovozni kompyuterga kiritadi?</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>Mikrofon</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Karnay</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Monitor</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>Printer</t>
-        </is>
-      </c>
+          <t>RAQAMLI QULF: Ikkilik sanoq tizimidagi 1010 sonini oʻnlik tizimga oʻtkazing. Natija — qulf kodi.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Mikrofon — ovozli kiritish qurilmasi.</t>
+          <t>1010₂ = 1·8 + 0·4 + 1·2 + 0·1 = 10.</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Unga gapiriladi.</t>
+          <t>Razryadlar qiymati chapdan oʻngga: 8, 4, 2, 1.</t>
         </is>
       </c>
       <c r="M86" s="2" t="n"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>oson</t>
+          <t>qiyin</t>
         </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P86" s="2" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q86" s="2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -7086,52 +7050,36 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Kiritish qurilmalari</t>
+          <t>Kompyuter tizimining asosiy komponentlari</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Qisqa javob</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Smartfon ekrani telefon burilganda ham aylanishi uchun qaysi sensor ishlaydi?</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Barmoq izi skaneri</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Termometr</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Akselerometr</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Mikrofon</t>
-        </is>
-      </c>
+          <t>QULF KODI: 1 bayt = 8 bit. 4 bayt necha bitga teng? Javobni raqam bilan kiriting.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Akselerometr qurilmaning holati va harakatini aniqlaydi.</t>
+          <t>4 × 8 = 32 bit.</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>U tezlanishni oʻlchaydi.</t>
+          <t>4 ni 8 ga koʻpaytiring.</t>
         </is>
       </c>
       <c r="M87" s="2" t="n"/>
@@ -7141,13 +7089,13 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
@@ -7161,7 +7109,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Saqlash qurilmalari va maʼlumot almashish</t>
+          <t>Chiqarish qurilmalari</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -7171,58 +7119,58 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>USB fleshka qanday xotira turiga asoslangan?</t>
+          <t>NOSOZLIK: kompyuter yoqildi, ventilyator aylanyapti, lekin monitor qop-qora. Birinchi navbatda nimani tekshirish kerak?</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Flesh-xotira (qattiq jismli)</t>
+          <t>Klaviatura tugmalarini</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Magnit disk</t>
+          <t>Internet tezligini</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Optik disk</t>
+          <t>Monitor kabeli ulanganini va monitor yoqilganini</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Magnit lenta</t>
+          <t>Printer siyohini</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Fleshka — flesh-xotira mikrosxemasiga ega qattiq jismli qurilma.</t>
+          <t>Eng oddiy sabablardan boshlash kerak: monitor quvvati va video kabel ulanishi.</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Nomi oʻzida.</t>
+          <t>Eng oddiy sababdan boshlang.</t>
         </is>
       </c>
       <c r="M88" s="2" t="n"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>oson</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
@@ -7236,7 +7184,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Saqlash qurilmalari va maʼlumot almashish</t>
+          <t>Chiqarish qurilmalari</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -7246,58 +7194,58 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Bluetooth nima uchun ishlatiladi?</t>
+          <t>NOSOZLIK: printer “Qogʻoz tiqilib qoldi” xabarini bermoqda. Toʻgʻri harakat qaysi?</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Qurilmalar orasida qisqa masofada simsiz maʼlumot almashish uchun</t>
+          <t>Kompyuterni formatlash</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Uzoq masofaga elektr energiyasini uzatish uchun</t>
+          <t>Printerni qattiq silkitish</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Maʼlumotni magnit lentaga yozish uchun</t>
+          <t>Printerni oʻchirib, tiqilgan qogʻozni ehtiyotkorlik bilan chiqarish</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Hujjatlarni chop etish uchun</t>
+          <t>Yangi monitor sotib olish</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Bluetooth — qisqa masofali (odatda 10 m atrofida) simsiz aloqa texnologiyasi.</t>
+          <t>Avval qurilmani xavfsiz holatga keltirib, qogʻozni yirtmasdan chiqarish kerak.</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Simsiz quloqchinlar shu orqali ulanadi.</t>
+          <t>Xavfsizlik birinchi oʻrinda.</t>
         </is>
       </c>
       <c r="M89" s="2" t="n"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>oʻrta</t>
+          <t>oson</t>
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P89" s="2" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q89" s="2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
@@ -7311,7 +7259,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter turlari</t>
+          <t>Kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -7321,27 +7269,27 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Qaysi qurilma eng koʻchma (mobil) hisoblanadi?</t>
+          <t>NOSOZLIK: sichqoncha kursori ekranda harakatlanmayapti. Eng oddiy birinchi qadam qaysi?</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Server shkafi</t>
+          <t>Monitorni oʻchirib qoʻyish</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Smartfon</t>
+          <t>Sichqoncha ulanishini yoki batareyasini tekshirish</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Mainframe</t>
+          <t>Protsessorni almashtirish</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Stol kompyuteri</t>
+          <t>Operatsion tizimni qayta oʻrnatish</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -7351,12 +7299,12 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Smartfon choʻntakka sigʻadi va doimiy internetga ulanishi mumkin.</t>
+          <t>Koʻp hollarda sabab oddiy: kabel chiqib qolgan yoki simsiz sichqoncha batareyasi tugagan.</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>U choʻntakka sigʻadi.</t>
+          <t>Simsiz sichqonchaga nima kerak?</t>
         </is>
       </c>
       <c r="M90" s="2" t="n"/>
@@ -7366,13 +7314,13 @@
         </is>
       </c>
       <c r="O90" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="Q90" s="2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
@@ -7386,37 +7334,37 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter tizimining asosiy komponentlari</t>
+          <t>Saqlash qurilmalarining afzallik va kamchiliklari</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Mantiqiy</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Ketma-ketlikni davom ettiring: 1, 2, 4, 8, 16, ?</t>
+          <t>NOSOZLIK: noutbuk juda sekinlashgan, qattiq disk deyarli toʻlib qolgan. Eng toʻgʻri yechim qaysi?</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>Klaviaturani almashtirish</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Wi-Fi ni oʻchirib qoʻyish</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Ekran yorugʻligini oshirish</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Keraksiz fayllarni oʻchirish yoki ularni tashqi/bulutli xotiraga koʻchirish</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -7426,12 +7374,12 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Har bir son oldingisidan 2 marta katta. Bu ikkilik sanoq tizimidagi razryad qiymatlari: 2⁰, 2¹, 2², …</t>
+          <t>Diskda boʻsh joy yetishmasa, tizim sekinlashadi. Joy boʻshatish yoki maʼlumotni boshqa xotiraga koʻchirish kerak.</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Har safar ikkiga koʻpaytiring.</t>
+          <t>Muammo xotirada.</t>
         </is>
       </c>
       <c r="M91" s="2" t="n"/>
@@ -7461,42 +7409,58 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter tizimining asosiy komponentlari</t>
+          <t>Kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Qisqa javob</t>
+          <t>Mantiqiy</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>RAQAMLI QULF: Ikkilik sanoq tizimidagi 1010 sonini oʻnlik tizimga oʻtkazing. Natija — qulf kodi.</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="n"/>
-      <c r="I92" s="2" t="n"/>
+          <t>MANTIQ: qurilma maʼlumotni kompyuterga KIRITADI va kompyuterdan CHIQARADI ham. Bu qaysi qurilma boʻlishi mumkin?</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Sensorli ekran</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Skaner</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Klaviatura</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Karnay</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>1010₂ = 1·8 + 0·4 + 1·2 + 0·1 = 10.</t>
+          <t>Sensorli ekran teginishni qabul qiladi (kiritish) va tasvirni koʻrsatadi (chiqarish).</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Razryadlar qiymati chapdan oʻngga: 8, 4, 2, 1.</t>
+          <t>Smartfon ekranini eslang.</t>
         </is>
       </c>
       <c r="M92" s="2" t="n"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>qiyin</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O92" s="2" t="n">
@@ -7525,12 +7489,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Qisqa javob</t>
+          <t>Toʻgʻri/Notoʻgʻri</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>QULF KODI: 1 bayt = 8 bit. 4 bayt necha bitga teng? Javobni raqam bilan kiriting.</t>
+          <t>Kompyuter oʻchganda ROMdagi maʼlumotlar yoʻqoladi.</t>
         </is>
       </c>
       <c r="F93" s="2" t="n"/>
@@ -7539,23 +7503,23 @@
       <c r="I93" s="2" t="n"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Notoʻgʻri</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>4 × 8 = 32 bit.</t>
+          <t>Notoʻgʻri. ROM — doimiy xotira, undagi maʼlumot elektr oʻchganda ham saqlanadi.</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>4 ni 8 ga koʻpaytiring.</t>
+          <t>ROM qanday xotira?</t>
         </is>
       </c>
       <c r="M93" s="2" t="n"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>oʻrta</t>
+          <t>oson</t>
         </is>
       </c>
       <c r="O93" s="2" t="n">
@@ -7579,52 +7543,36 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Chiqarish qurilmalari</t>
+          <t>Saqlash qurilmalarining afzallik va kamchiliklari</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Toʻgʻri/Notoʻgʻri</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>NOSOZLIK: kompyuter yoqildi, ventilyator aylanyapti, lekin monitor qop-qora. Birinchi navbatda nimani tekshirish kerak?</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Klaviatura tugmalarini</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Internet tezligini</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Monitor kabeli ulanganini va monitor yoqilganini</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>Printer siyohini</t>
-        </is>
-      </c>
+          <t>HDD harakatlanuvchi mexanik qismlarga ega, shuning uchun u SSDga qaraganda zarbaga sezgirroq.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Toʻgʻri</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Eng oddiy sabablardan boshlash kerak: monitor quvvati va video kabel ulanishi.</t>
+          <t>Toʻgʻri. Zarba paytida HDD kallagi aylanuvchi plastinaga tegib, uni shikastlashi mumkin.</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Eng oddiy sababdan boshlang.</t>
+          <t>Qaysi biri ichida aylanadi?</t>
         </is>
       </c>
       <c r="M94" s="2" t="n"/>
@@ -7654,58 +7602,58 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Chiqarish qurilmalari</t>
+          <t>Kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Mantiqiy</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>NOSOZLIK: printer “Qogʻoz tiqilib qoldi” xabarini bermoqda. Toʻgʻri harakat qaysi?</t>
+          <t>MANTIQ: qaysi qatordagi BARCHA qurilmalar kiritish qurilmalari?</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Kompyuterni formatlash</t>
+          <t>Monitor, printer, karnay</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Printerni qattiq silkitish</t>
+          <t>Klaviatura, mikrofon, skaner</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Printerni oʻchirib, tiqilgan qogʻozni ehtiyotkorlik bilan chiqarish</t>
+          <t>Mikrofon, karnay, proyektor</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Yangi monitor sotib olish</t>
+          <t>Klaviatura, monitor, printer</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Avval qurilmani xavfsiz holatga keltirib, qogʻozni yirtmasdan chiqarish kerak.</t>
+          <t>Klaviatura, mikrofon va skaner maʼlumotni kompyuterga kiritadi.</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Xavfsizlik birinchi oʻrinda.</t>
+          <t>Har bir qurilma kompyuterga nimadir “beradimi”?</t>
         </is>
       </c>
       <c r="M95" s="2" t="n"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>oson</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O95" s="2" t="n">
@@ -7729,37 +7677,37 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Kiritish qurilmalari</t>
+          <t>Saqlash qurilmalari va maʼlumot almashish</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Mantiqiy</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>NOSOZLIK: sichqoncha kursori ekranda harakatlanmayapti. Eng oddiy birinchi qadam qaysi?</t>
+          <t>MANTIQ: qaysi qatorda optik disklar sigʻimi KICHIKDAN KATTAGA toʻgʻri tartiblangan?</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Monitorni oʻchirib qoʻyish</t>
+          <t>Blu-ray → DVD → CD</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Sichqoncha ulanishini yoki batareyasini tekshirish</t>
+          <t>CD → DVD → Blu-ray</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Protsessorni almashtirish</t>
+          <t>CD → Blu-ray → DVD</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Operatsion tizimni qayta oʻrnatish</t>
+          <t>DVD → CD → Blu-ray</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -7769,18 +7717,18 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Koʻp hollarda sabab oddiy: kabel chiqib qolgan yoki simsiz sichqoncha batareyasi tugagan.</t>
+          <t>CD ≈ 700 MB &lt; DVD ≈ 4,7 GB &lt; Blu-ray ≈ 25 GB.</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Simsiz sichqonchaga nima kerak?</t>
+          <t>Eng eskisi — eng kichigi.</t>
         </is>
       </c>
       <c r="M96" s="2" t="n"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>oson</t>
+          <t>qiyin</t>
         </is>
       </c>
       <c r="O96" s="2" t="n">
@@ -7804,52 +7752,36 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Saqlash qurilmalarining afzallik va kamchiliklari</t>
+          <t>Kompyuter tizimining asosiy komponentlari</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Qisqa javob</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>NOSOZLIK: noutbuk juda sekinlashgan, qattiq disk deyarli toʻlib qolgan. Eng toʻgʻri yechim qaysi?</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Klaviaturani almashtirish</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Wi-Fi ni oʻchirib qoʻyish</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Ekran yorugʻligini oshirish</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>Keraksiz fayllarni oʻchirish yoki ularni tashqi/bulutli xotiraga koʻchirish</t>
-        </is>
-      </c>
+          <t>QULF KODI: ketma-ketlikning keyingi sonini kiriting: 3, 6, 12, 24, ?</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="2" t="n"/>
+      <c r="H97" s="2" t="n"/>
+      <c r="I97" s="2" t="n"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Diskda boʻsh joy yetishmasa, tizim sekinlashadi. Joy boʻshatish yoki maʼlumotni boshqa xotiraga koʻchirish kerak.</t>
+          <t>Har bir son oldingisidan 2 marta katta: 24 × 2 = 48.</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Muammo xotirada.</t>
+          <t>Oldingi sonni ikkiga koʻpaytiring.</t>
         </is>
       </c>
       <c r="M97" s="2" t="n"/>
@@ -7879,58 +7811,42 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Kiritish qurilmalari</t>
+          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Mantiqiy</t>
+          <t>Qisqa javob</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>MANTIQ: qurilma maʼlumotni kompyuterga KIRITADI va kompyuterdan CHIQARADI ham. Bu qaysi qurilma boʻlishi mumkin?</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Sensorli ekran</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Skaner</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Klaviatura</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>Karnay</t>
-        </is>
-      </c>
+          <t>PAROL: bank cheklaridagi magnit siyohli raqamlarni oʻqiydigan texnologiyaning 4 harfli qisqartmasini yozing.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MICR</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Sensorli ekran teginishni qabul qiladi (kiritish) va tasvirni koʻrsatadi (chiqarish).</t>
+          <t>MICR — Magnetic Ink Character Recognition.</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Smartfon ekranini eslang.</t>
+          <t>M… I… C… R…</t>
         </is>
       </c>
       <c r="M98" s="2" t="n"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>oʻrta</t>
+          <t>qiyin</t>
         </is>
       </c>
       <c r="O98" s="2" t="n">
@@ -7954,42 +7870,58 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter tizimining asosiy komponentlari</t>
+          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Toʻgʻri/Notoʻgʻri</t>
+          <t>Mantiqiy</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter oʻchganda ROMdagi maʼlumotlar yoʻqoladi.</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="n"/>
-      <c r="G99" s="2" t="n"/>
-      <c r="H99" s="2" t="n"/>
-      <c r="I99" s="2" t="n"/>
+          <t>MANTIQ: kassir tovarni skanerlaydi, ekranda narx chiqadi va chek chop etiladi. Qurilmalar qaysi tartibda ishladi?</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Ekran → shtrix-kod oʻquvchi → printer</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Shtrix-kod oʻquvchi → protsessor → ekran va printer</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Printer → protsessor → shtrix-kod oʻquvchi</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Protsessor → printer → shtrix-kod oʻquvchi</t>
+        </is>
+      </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Notoʻgʻri</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Notoʻgʻri. ROM — doimiy xotira, undagi maʼlumot elektr oʻchganda ham saqlanadi.</t>
+          <t>Kiritish (shtrix-kod) → qayta ishlash (protsessor narxni topadi) → chiqarish (ekran va chek printeri).</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>ROM qanday xotira?</t>
+          <t>Kiritish → qayta ishlash → chiqarish.</t>
         </is>
       </c>
       <c r="M99" s="2" t="n"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>oson</t>
+          <t>qiyin</t>
         </is>
       </c>
       <c r="O99" s="2" t="n">
@@ -8013,7 +7945,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Saqlash qurilmalarining afzallik va kamchiliklari</t>
+          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -8023,7 +7955,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>HDD harakatlanuvchi mexanik qismlarga ega, shuning uchun u SSDga qaraganda zarbaga sezgirroq.</t>
+          <t>OCR texnologiyasi skanerlangan bosma matnni tahrirlanadigan matnga aylantira oladi.</t>
         </is>
       </c>
       <c r="F100" s="2" t="n"/>
@@ -8037,12 +7969,12 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Toʻgʻri. Zarba paytida HDD kallagi aylanuvchi plastinaga tegib, uni shikastlashi mumkin.</t>
+          <t>Toʻgʻri. OCR tasvirdagi harflarni taniydi.</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Qaysi biri ichida aylanadi?</t>
+          <t>C — Character.</t>
         </is>
       </c>
       <c r="M100" s="2" t="n"/>
@@ -8072,68 +8004,68 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Kiritish qurilmalari</t>
+          <t>Saqlash qurilmalarining afzallik va kamchiliklari</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Mantiqiy</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>MANTIQ: qaysi qatordagi BARCHA qurilmalar kiritish qurilmalari?</t>
+          <t>Qaysi vaziyatda magnit lenta eng mos saqlash vositasi hisoblanadi?</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Monitor, printer, karnay</t>
+          <t>Doʻstga bitta faylni tez uzatish</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Klaviatura, mikrofon, skaner</t>
+          <t>Kompyuter oʻyinlarini tez yuklash</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Mikrofon, karnay, proyektor</t>
+          <t>Yirik tashkilotning har kungi toʻliq zaxira nusxasini arzon saqlash</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Klaviatura, monitor, printer</t>
+          <t>Smartfonda tez-tez ochiladigan rasmlarni saqlash</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Klaviatura, mikrofon va skaner maʼlumotni kompyuterga kiritadi.</t>
+          <t>Lenta katta hajmni arzon saqlaydi, zaxira nusxadan esa kamdan-kam va ketma-ket foydalaniladi.</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Har bir qurilma kompyuterga nimadir “beradimi”?</t>
+          <t>Zaxira nusxa (backup) haqida oʻylang.</t>
         </is>
       </c>
       <c r="M101" s="2" t="n"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>oʻrta</t>
+          <t>qiyin</t>
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P101" s="2" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="Q101" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="102">
@@ -8147,52 +8079,52 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Saqlash qurilmalari va maʼlumot almashish</t>
+          <t>Kompyuter tizimining asosiy komponentlari</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Mantiqiy</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>MANTIQ: qaysi qatorda optik disklar sigʻimi KICHIKDAN KATTAGA toʻgʻri tartiblangan?</t>
+          <t>Nima uchun kompyuterni yuklovchi dastur RAMda emas, balki ROMda saqlanadi?</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Blu-ray → DVD → CD</t>
+          <t>Chunki u elektr oʻchganda ham yoʻqolmasligi kerak</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>CD → DVD → Blu-ray</t>
+          <t>Chunki ROMga foydalanuvchi oʻyinlarini yozadi</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>CD → Blu-ray → DVD</t>
+          <t>Chunki RAM juda sekin ishlaydi</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>DVD → CD → Blu-ray</t>
+          <t>Chunki RAM faqat rasmlarni saqlaydi</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>CD ≈ 700 MB &lt; DVD ≈ 4,7 GB &lt; Blu-ray ≈ 25 GB.</t>
+          <t>Kompyuter yoqilishi bilan ishga tushirish dasturi tayyor turishi kerak — buni faqat doimiy xotira (ROM) taʼminlaydi.</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Eng eskisi — eng kichigi.</t>
+          <t>RAM va ROMning asosiy farqi nimada?</t>
         </is>
       </c>
       <c r="M102" s="2" t="n"/>
@@ -8202,13 +8134,13 @@
         </is>
       </c>
       <c r="O102" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="Q102" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103">
@@ -8222,52 +8154,68 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter tizimining asosiy komponentlari</t>
+          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Qisqa javob</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>QULF KODI: ketma-ketlikning keyingi sonini kiriting: 3, 6, 12, 24, ?</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="2" t="n"/>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="n"/>
+          <t>Kutubxona javondagi kitoblarni har birini qoʻlga olmasdan, masofadan hisobga olmoqchi. Qaysi texnologiya eng mos?</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>OMR</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>MICR</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>RFID</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Shtrix-kod</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>Har bir son oldingisidan 2 marta katta: 24 × 2 = 48.</t>
+          <t>RFID yorliqlari radiotoʻlqin orqali oʻqiladi va toʻgʻridan-toʻgʻri koʻrinishni talab qilmaydi; bir vaqtda koʻp yorliqni oʻqish mumkin.</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Oldingi sonni ikkiga koʻpaytiring.</t>
+          <t>Bu texnologiya radiotoʻlqindan foydalanadi.</t>
         </is>
       </c>
       <c r="M103" s="2" t="n"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>oʻrta</t>
+          <t>qiyin</t>
         </is>
       </c>
       <c r="O103" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="Q103" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104">
@@ -8281,36 +8229,52 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
+          <t>Kompyuter turlari</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Qisqa javob</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>PAROL: bank cheklaridagi magnit siyohli raqamlarni oʻqiydigan texnologiyaning 4 harfli qisqartmasini yozing.</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="2" t="n"/>
-      <c r="H104" s="2" t="n"/>
-      <c r="I104" s="2" t="n"/>
+          <t>Ilmiy markaz har kuni ulkan hajmdagi ob-havo maʼlumotlarini juda tez hisoblashi kerak. Qaysi kompyuter turi eng mos?</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Smart soat</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Superkompyuter</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Planshet</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Noutbuk</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>MICR</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>MICR — Magnetic Ink Character Recognition.</t>
+          <t>Superkompyuterlar soniyasiga trillionlab amal bajaradi va ob-havo modellashtirishda ishlatiladi.</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>M… I… C… R…</t>
+          <t>Eng kuchli kompyuter turi.</t>
         </is>
       </c>
       <c r="M104" s="2" t="n"/>
@@ -8320,13 +8284,13 @@
         </is>
       </c>
       <c r="O104" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="Q104" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="105">
@@ -8340,47 +8304,47 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
+          <t>Kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Mantiqiy</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>MANTIQ: kassir tovarni skanerlaydi, ekranda narx chiqadi va chek chop etiladi. Qurilmalar qaysi tartibda ishladi?</t>
+          <t>Shifoxonada bemorning yurak urishi doimiy kuzatiladi va xavfli holatda signal chalinadi. Bu tizimda qaysi qurilmalar ishlaydi?</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Ekran → shtrix-kod oʻquvchi → printer</t>
+          <t>Faqat klaviatura</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Shtrix-kod oʻquvchi → protsessor → ekran va printer</t>
+          <t>Faqat printer</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Printer → protsessor → shtrix-kod oʻquvchi</t>
+          <t>Sensor (kiritish) hamda ekran va signal (chiqarish)</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Protsessor → printer → shtrix-kod oʻquvchi</t>
+          <t>Faqat DVD disk</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Kiritish (shtrix-kod) → qayta ishlash (protsessor narxni topadi) → chiqarish (ekran va chek printeri).</t>
+          <t>Sensor maʼlumotni uzluksiz kiritadi, kompyuter uni tahlil qiladi, ekran va signal esa natijani chiqaradi.</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
@@ -8395,13 +8359,13 @@
         </is>
       </c>
       <c r="O105" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="Q105" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="106">
@@ -8415,36 +8379,52 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
+          <t>Yangi texnologiyalarning taʼsiri</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Toʻgʻri/Notoʻgʻri</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>OCR texnologiyasi skanerlangan bosma matnni tahrirlanadigan matnga aylantira oladi.</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="n"/>
-      <c r="I106" s="2" t="n"/>
+          <t>Sunʼiy intellekt keng qoʻllanilishining salbiy taʼsirlaridan biri qaysi?</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Internetning yoʻqolib ketishi</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Baʼzi kasblarda ish oʻrinlarining qisqarishi</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Kompyuterlarning butunlay ishlamay qolishi</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Elektr energiyasining bepul boʻlib qolishi</t>
+        </is>
+      </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Toʻgʻri</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Toʻgʻri. OCR tasvirdagi harflarni taniydi.</t>
+          <t>Avtomatlashtirish takroriy ishlarda inson mehnatiga ehtiyojni kamaytiradi, ammo yangi kasblar ham paydo boʻladi.</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>C — Character.</t>
+          <t>Mehnat bozori haqida oʻylang.</t>
         </is>
       </c>
       <c r="M106" s="2" t="n"/>
@@ -8454,13 +8434,13 @@
         </is>
       </c>
       <c r="O106" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P106" s="2" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="Q106" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="107">
@@ -8484,42 +8464,42 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Qaysi vaziyatda magnit lenta eng mos saqlash vositasi hisoblanadi?</t>
+          <t>Fotograf 200 GB fotosuratni mijozga tez yetkazmoqchi, lekin internet juda sekin. Eng qulay yechim qaysi?</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Doʻstga bitta faylni tez uzatish</t>
+          <t>Tashqi SSD yoki katta sigʻimli fleshka</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter oʻyinlarini tez yuklash</t>
+          <t>300 ta CD disk</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Yirik tashkilotning har kungi toʻliq zaxira nusxasini arzon saqlash</t>
+          <t>Magnit lenta</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Smartfonda tez-tez ochiladigan rasmlarni saqlash</t>
+          <t>Har bir rasmni elektron pochtada alohida yuborish</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Lenta katta hajmni arzon saqlaydi, zaxira nusxadan esa kamdan-kam va ketma-ket foydalaniladi.</t>
+          <t>Koʻchma SSD/fleshka katta hajmni tez yozadi va oʻqiydi, internetga bogʻliq emas.</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Zaxira nusxa (backup) haqida oʻylang.</t>
+          <t>Tezkor va koʻchma xotira kerak.</t>
         </is>
       </c>
       <c r="M107" s="2" t="n"/>
@@ -8549,7 +8529,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter tizimining asosiy komponentlari</t>
+          <t>Operatsion tizimlar</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -8559,42 +8539,42 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Nima uchun kompyuterni yuklovchi dastur RAMda emas, balki ROMda saqlanadi?</t>
+          <t>Koʻrish qobiliyati cheklangan foydalanuvchi uchun qaysi interfeys eng qulay boʻlishi mumkin?</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Chunki u elektr oʻchganda ham yoʻqolmasligi kerak</t>
+          <t>Faqat sichqoncha bilan boshqaruv</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Chunki ROMga foydalanuvchi oʻyinlarini yozadi</t>
+          <t>Faqat mayda shriftli buyruqlar satri</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Chunki RAM juda sekin ishlaydi</t>
+          <t>Ovozli boshqaruv interfeysi</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Chunki RAM faqat rasmlarni saqlaydi</t>
+          <t>Faqat kichik ikonkali grafik menyu</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter yoqilishi bilan ishga tushirish dasturi tayyor turishi kerak — buni faqat doimiy xotira (ROM) taʼminlaydi.</t>
+          <t>Ovozli interfeys ekranga qaramasdan buyruq berish va javobni eshitish imkonini beradi.</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>RAM va ROMning asosiy farqi nimada?</t>
+          <t>Koʻz oʻrniga qaysi sezgi ishlatiladi?</t>
         </is>
       </c>
       <c r="M108" s="2" t="n"/>
@@ -8624,52 +8604,36 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
+          <t>Kompyuter tizimining asosiy komponentlari</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Qisqa javob</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Kutubxona javondagi kitoblarni har birini qoʻlga olmasdan, masofadan hisobga olmoqchi. Qaysi texnologiya eng mos?</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>OMR</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>MICR</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>RFID</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>Shtrix-kod</t>
-        </is>
-      </c>
+          <t>BOSS QULFI: ikkilik sanoq tizimidagi 1111 sonini oʻnlik tizimga oʻtkazing.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n"/>
+      <c r="G109" s="2" t="n"/>
+      <c r="H109" s="2" t="n"/>
+      <c r="I109" s="2" t="n"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>RFID yorliqlari radiotoʻlqin orqali oʻqiladi va toʻgʻridan-toʻgʻri koʻrinishni talab qilmaydi; bir vaqtda koʻp yorliqni oʻqish mumkin.</t>
+          <t>1111₂ = 8 + 4 + 2 + 1 = 15.</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Bu texnologiya radiotoʻlqindan foydalanadi.</t>
+          <t>Razryadlar qiymati: 8, 4, 2, 1.</t>
         </is>
       </c>
       <c r="M109" s="2" t="n"/>
@@ -8699,7 +8663,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter turlari</t>
+          <t>Saqlash qurilmalarining afzallik va kamchiliklari</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -8709,42 +8673,42 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Ilmiy markaz har kuni ulkan hajmdagi ob-havo maʼlumotlarini juda tez hisoblashi kerak. Qaysi kompyuter turi eng mos?</t>
+          <t>Nima uchun planshetlarda HDD emas, balki flesh-xotira ishlatiladi?</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Smart soat</t>
+          <t>U yengil, kam energiya sarflaydi va zarbaga chidamli</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Superkompyuter</t>
+          <t>U har doim HDDdan arzonroq</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Planshet</t>
+          <t>U magnit maydonida yaxshiroq ishlaydi</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Noutbuk</t>
+          <t>Unga faqat bir marta yozish mumkin</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Superkompyuterlar soniyasiga trillionlab amal bajaradi va ob-havo modellashtirishda ishlatiladi.</t>
+          <t>Mobil qurilmalarda vazn, batareya sarfi va chidamlilik muhim — flesh-xotira bularning barchasida ustun.</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Eng kuchli kompyuter turi.</t>
+          <t>Planshet tushib ketsa nima boʻladi?</t>
         </is>
       </c>
       <c r="M110" s="2" t="n"/>
@@ -8774,52 +8738,52 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Kiritish qurilmalari</t>
+          <t>Operatsion tizimlar</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Mantiqiy</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Shifoxonada bemorning yurak urishi doimiy kuzatiladi va xavfli holatda signal chalinadi. Bu tizimda qaysi qurilmalar ishlaydi?</t>
+          <t>Operatsion tizimning qaysi funksiyasi bir vaqtda bir nechta dastur ishlashini taʼminlaydi?</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Faqat klaviatura</t>
+          <t>Faqat fayllarni oʻchirish</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Faqat printer</t>
+          <t>Printerga siyoh qoʻshish</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Sensor (kiritish) hamda ekran va signal (chiqarish)</t>
+          <t>Ekran yorugʻligini oshirish</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Faqat DVD disk</t>
+          <t>Jarayonlar va xotirani boshqarish (koʻp vazifalilik)</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>Sensor maʼlumotni uzluksiz kiritadi, kompyuter uni tahlil qiladi, ekran va signal esa natijani chiqaradi.</t>
+          <t>OT protsessor vaqtini va xotirani dasturlar orasida taqsimlaydi — bu multitasking.</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Kiritish → qayta ishlash → chiqarish.</t>
+          <t>Musiqa tinglab, bir vaqtda matn yozish.</t>
         </is>
       </c>
       <c r="M111" s="2" t="n"/>
@@ -8859,42 +8823,42 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Sunʼiy intellekt keng qoʻllanilishining salbiy taʼsirlaridan biri qaysi?</t>
+          <t>Qaysi texnologiya ishlab chiqarishda ham, tibbiyotda ham (masalan, protez yasashda) katta oʻzgarish yasadi?</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Internetning yoʻqolib ketishi</t>
+          <t>Elektron-nurli (CRT) monitor</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Baʼzi kasblarda ish oʻrinlarining qisqarishi</t>
+          <t>Disketa</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Kompyuterlarning butunlay ishlamay qolishi</t>
+          <t>3D chop etish</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Elektr energiyasining bepul boʻlib qolishi</t>
+          <t>Matritsali printer</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>Avtomatlashtirish takroriy ishlarda inson mehnatiga ehtiyojni kamaytiradi, ammo yangi kasblar ham paydo boʻladi.</t>
+          <t>3D printerlar shaxsga moslashtirilgan protezlar, ehtiyot qismlar va prototiplarni tez yasash imkonini beradi.</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Mehnat bozori haqida oʻylang.</t>
+          <t>U qatlamma-qatlam “quradi”.</t>
         </is>
       </c>
       <c r="M112" s="2" t="n"/>
@@ -8924,68 +8888,64 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Saqlash qurilmalarining afzallik va kamchiliklari</t>
+          <t>Kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Moslashtirish</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Fotograf 200 GB fotosuratni mijozga tez yetkazmoqchi, lekin internet juda sekin. Eng qulay yechim qaysi?</t>
+          <t>MOSLASHTIRISH: Qurilmalarni vazifasiga moslang.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Tashqi SSD yoki katta sigʻimli fleshka</t>
+          <t>Klaviatura = Kiritish</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>300 ta CD disk</t>
+          <t>Printer = Chiqarish</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Magnit lenta</t>
+          <t>Fleshka = Saqlash</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Har bir rasmni elektron pochtada alohida yuborish</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>Mikrofon = Kiritish</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n"/>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>Koʻchma SSD/fleshka katta hajmni tez yozadi va oʻqiydi, internetga bogʻliq emas.</t>
+          <t>Kiritish qurilmalari maʼlumotni kompyuterga kiritadi, chiqarish qurilmalari natijani koʻrsatadi, saqlash qurilmalari maʼlumotni uzoq saqlaydi.</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Tezkor va koʻchma xotira kerak.</t>
+          <t>Maʼlumot qaysi tomonga harakatlanadi?</t>
         </is>
       </c>
       <c r="M113" s="2" t="n"/>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>qiyin</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P113" s="2" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="Q113" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114">
@@ -8999,68 +8959,64 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Operatsion tizimlar</t>
+          <t>Saqlash qurilmalari va maʼlumot almashish</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Moslashtirish</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Koʻrish qobiliyati cheklangan foydalanuvchi uchun qaysi interfeys eng qulay boʻlishi mumkin?</t>
+          <t>MOSLASHTIRISH: Saqlash qurilmalarini ishlash usuliga moslang.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Faqat sichqoncha bilan boshqaruv</t>
+          <t>Qattiq disk (HDD) = Magnit</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Faqat mayda shriftli buyruqlar satri</t>
+          <t>DVD disk = Optik (lazer)</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Ovozli boshqaruv interfeysi</t>
+          <t>SSD = Flesh-xotira</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Faqat kichik ikonkali grafik menyu</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>Magnit lenta = Magnit</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>Ovozli interfeys ekranga qaramasdan buyruq berish va javobni eshitish imkonini beradi.</t>
+          <t>HDD va lenta maʼlumotni magnitlangan sirtga yozadi, CD/DVD lazer nuri bilan oʻqiladi, SSD va fleshka esa harakatlanuvchi qismlarsiz flesh-xotiradan foydalanadi.</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Koʻz oʻrniga qaysi sezgi ishlatiladi?</t>
+          <t>Magnit, lazer yoki mikrosxema?</t>
         </is>
       </c>
       <c r="M114" s="2" t="n"/>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>qiyin</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O114" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115">
@@ -9074,52 +9030,64 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Kompyuter tizimining asosiy komponentlari</t>
+          <t>Kompyuter qurilmalari va dasturiy taʼminot</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Qisqa javob</t>
+          <t>Moslashtirish</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>BOSS QULFI: ikkilik sanoq tizimidagi 1111 sonini oʻnlik tizimga oʻtkazing.</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="n"/>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="n"/>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>MOSLASHTIRISH: Dasturlarni turiga moslang.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Windows = Operatsion tizim</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Matn muharriri = Amaliy dastur</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Antivirus = Utilita (xizmat dasturi)</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Linux = Operatsion tizim</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n"/>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>1111₂ = 8 + 4 + 2 + 1 = 15.</t>
+          <t>Operatsion tizim kompyuterni boshqaradi, amaliy dasturlar foydalanuvchi vazifasini bajaradi, utilitalar esa tizimga xizmat koʻrsatadi (himoya, tozalash, arxivlash).</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Razryadlar qiymati: 8, 4, 2, 1.</t>
+          <t>Kim kompyuterni boshqaradi, kim foydalanuvchiga xizmat qiladi?</t>
         </is>
       </c>
       <c r="M115" s="2" t="n"/>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>qiyin</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P115" s="2" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="Q115" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116">
@@ -9133,52 +9101,48 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Saqlash qurilmalarining afzallik va kamchiliklari</t>
+          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Moslashtirish</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Nima uchun planshetlarda HDD emas, balki flesh-xotira ishlatiladi?</t>
+          <t>MOSLASHTIRISH: Bevosita kiritish usullarini qoʻllanish joyiga moslang.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>U yengil, kam energiya sarflaydi va zarbaga chidamli</t>
+          <t>Shtrix-kod skaneri = Doʻkon kassasi</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>U har doim HDDdan arzonroq</t>
+          <t>OMR = Test varaqalarini tekshirish</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>U magnit maydonida yaxshiroq ishlaydi</t>
+          <t>RFID = Kontaktsiz kirish kartasi</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Unga faqat bir marta yozish mumkin</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>Chip va PIN = Bank kartasi bilan toʻlov</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Mobil qurilmalarda vazn, batareya sarfi va chidamlilik muhim — flesh-xotira bularning barchasida ustun.</t>
+          <t>Bevosita kiritish qurilmalari maʼlumotni klaviaturasiz, tez va xatosiz kiritadi: shtrix-kod — tovarlar, OMR — belgilangan javoblar, RFID — radio metkalar, chip va PIN — bank kartasi.</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Planshet tushib ketsa nima boʻladi?</t>
+          <t>Har bir texnologiya qayerda koʻp uchraydi?</t>
         </is>
       </c>
       <c r="M116" s="2" t="n"/>
@@ -9188,13 +9152,13 @@
         </is>
       </c>
       <c r="O116" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117">
@@ -9208,68 +9172,64 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Operatsion tizimlar</t>
+          <t>Kompyuter turlari</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Mantiqiy</t>
+          <t>Moslashtirish</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Operatsion tizimning qaysi funksiyasi bir vaqtda bir nechta dastur ishlashini taʼminlaydi?</t>
+          <t>MOSLASHTIRISH: Kompyuter turlarini tavsifiga moslang.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Faqat fayllarni oʻchirish</t>
+          <t>Mainframe = Minglab foydalanuvchiga xizmat qiluvchi kuchli kompyuter</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Printerga siyoh qoʻshish</t>
+          <t>Noutbuk = Batareyali koʻchma kompyuter</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Ekran yorugʻligini oshirish</t>
+          <t>Smartfon = Choʻntakdagi mobil qurilma</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Jarayonlar va xotirani boshqarish (koʻp vazifalilik)</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>Stol kompyuteri = Doimiy joyda turadigan shaxsiy kompyuter</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n"/>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>OT protsessor vaqtini va xotirani dasturlar orasida taqsimlaydi — bu multitasking.</t>
+          <t>Kompyuterlar oʻlchami, quvvati va koʻchmaligi boʻyicha farq qiladi.</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>Musiqa tinglab, bir vaqtda matn yozish.</t>
+          <t>Eng kattasi va eng kichigini toping.</t>
         </is>
       </c>
       <c r="M117" s="2" t="n"/>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>qiyin</t>
+          <t>oʻrta</t>
         </is>
       </c>
       <c r="O117" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P117" s="2" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="Q117" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="118">
@@ -9283,52 +9243,48 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Yangi texnologiyalarning taʼsiri</t>
+          <t>Chiqarish qurilmalari</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Koʻp bosqichli</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Qaysi texnologiya ishlab chiqarishda ham, tibbiyotda ham (masalan, protez yasashda) katta oʻzgarish yasadi?</t>
+          <t>NOSOZLIK ZANJIRI: Printer hujjatni chop etmayapti. Muammoni bosqichma-bosqich toping.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Elektron-nurli (CRT) monitor</t>
+          <t>Avval nimani tekshirasiz? || Printer yoqilgan va kompyuterga ulanganini | Monitor yorugʻligini | Kompyuter protsessorini</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Disketa</t>
+          <t>Printer yoqilgan va ulangan, lekin ekranda “Qogʻoz tugadi” xabari chiqdi. Nima qilasiz? || Klaviaturani almashtiraman | Operatsion tizimni qayta oʻrnataman | Lotokka qogʻoz solaman</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>3D chop etish</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>Matritsali printer</t>
-        </is>
-      </c>
+          <t>Qogʻoz solindi, lekin sahifa juda xira chiqyapti. Ehtimoliy sabab? || Sichqoncha buzilgan | Siyoh yoki toner tugayapti | Internet sekin</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A, C, B</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>3D printerlar shaxsga moslashtirilgan protezlar, ehtiyot qismlar va prototiplarni tez yasash imkonini beradi.</t>
+          <t>Nosozlik eng oddiy sabablardan boshlab tekshiriladi: quvvat va ulanish → qogʻoz → siyoh yoki toner.</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>U qatlamma-qatlam “quradi”.</t>
+          <t>Oddiydan murakkabga.</t>
         </is>
       </c>
       <c r="M118" s="2" t="n"/>
@@ -9338,20 +9294,233 @@
         </is>
       </c>
       <c r="O118" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P118" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Informatika</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Saqlash qurilmalari va maʼlumot almashish</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Koʻp bosqichli</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>RAQAMLI ZANJIR: Hajmi 2 GB boʻlgan videoni 8 GB lik fleshkaga yozmoqchisiz. Hisobni qadamma-qadam bajaring.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>1 GB necha MB ga teng? || 1000 KB | 8 MB | 1024 MB | 100 MB</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Demak, 2 GB lik video necha MB? || 4096 MB | 2048 MB | 1024 MB | 2000 KB</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>8 GB lik fleshkaga shunday videolardan nechtasi sigʻadi? || 2 ta | 16 ta | 8 ta | 4 ta</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>C, B, D</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>1 GB = 1024 MB, shuning uchun 2 GB = 2048 MB. 8 GB ÷ 2 GB = 4 ta video.</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>Har bir birlik oldingisidan 1024 marta katta.</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>qiyin</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P119" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q119" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Informatika</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Operatsion tizimlar</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Koʻp bosqichli</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>BOSS ZANJIRI: Kompyuter yoqilgandan to dastur ishga tushguncha nima sodir boʻladi?</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Kompyuter yoqilganda birinchi boʻlib nima ishga tushadi? || Brauzer | BIOS/UEFI — qurilmalarni tekshiradi | Matn muharriri</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Shundan keyin qaysi dastur xotiraga yuklanadi? || Antivirus bazasi | Fotosuratlar papkasi | Operatsion tizim</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Foydalanuvchi dastur belgisini bosganda uni nima ishga tushiradi? || Sichqoncha | Operatsion tizim — dasturni xotiraga yuklaydi | Monitor</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n"/>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>B, C, B</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Yuklanish ketma-ketligi: BIOS/UEFI qurilmalarni tekshiradi → operatsion tizim yuklanadi → OT foydalanuvchi dasturlarini xotiraga yuklab ishga tushiradi.</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>Avval apparat, keyin OT, keyin dasturlar.</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>qiyin</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P118" s="2" t="n">
+      <c r="P120" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="Q118" s="2" t="n">
+      <c r="Q120" s="2" t="n">
         <v>45</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Informatika</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Maʼlumotlarni bevosita kiritish qurilmalari</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Koʻp bosqichli</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>BOSS ZANJIRI: Xaridor doʻkonda tovar sotib olmoqda. Maʼlumot qanday harakatlanishini kuzating.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Kassir tovarni qanday tez kiritadi? || Nomini klaviaturada yozadi | Shtrix-kodni skaner bilan oʻqiydi | Mikrofonga aytadi</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Tovar narxi qayerdan olinadi? || Xaridorning telefonidan | Printer xotirasidan | Doʻkonning maʼlumotlar bazasidan</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Xaridor bank kartasi bilan toʻlaydi. Karta maʼlumoti qanday oʻqiladi? || Chip va PIN yoki kontaktsiz (NFC) terminal orqali | Kassir qoʻlda yozib | Skaner bilan rasmga olib</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>B, C, A</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Doʻkonda maʼlumot avtomatik kiritiladi: shtrix-kod → maʼlumotlar bazasidan narx → chip va PIN yoki NFC orqali toʻlov.</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>Har qadamda eng tez va xatosiz usulni tanlang.</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>qiyin</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P121" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q121" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q118"/>
+  <autoFilter ref="A1:Q121"/>
   <dataValidations count="6">
     <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Savol turi" error="Roʻyxatdan tanlang" type="list">
-      <formula1>"Test,Toʻgʻri/Notoʻgʻri,Rasmli,Qisqa javob,Mantiqiy"</formula1>
+      <formula1>"Test,Toʻgʻri/Notoʻgʻri,Rasmli,Qisqa javob,Mantiqiy,Moslashtirish,Koʻp bosqichli"</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Qiyinlik" error="oson, oʻrta yoki qiyin" type="list">
       <formula1>"oson,oʻrta,qiyin"</formula1>
@@ -9383,7 +9552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9515,7 +9684,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Roʻyxatdan tanlang: Test, Toʻgʻri/Notoʻgʻri, Rasmli, Qisqa javob, Mantiqiy.</t>
+          <t>Roʻyxatdan tanlang: Test, Toʻgʻri/Notoʻgʻri, Rasmli, Qisqa javob, Mantiqiy, Moslashtirish, Koʻp bosqichli.</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9708,9 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Test, Rasmli va Mantiqiy savollar uchun variantlar. Kamida A va B toʻldirilsin.</t>
+          <t>Test, Rasmli va Mantiqiy savollar uchun variantlar. Kamida A va B toʻldirilsin.
+Moslashtirish: har bir katakda juftlik “Chap = Oʻng” (masalan: Klaviatura = Kiritish).
+Koʻp bosqichli: har bir katak — bitta qadam “Qadam matni || variant | variant | variant”.</t>
         </is>
       </c>
     </row>
@@ -9589,7 +9760,9 @@
         <is>
           <t>Test/Rasmli/Mantiqiy: A, B, C yoki D.
 Toʻgʻri/Notoʻgʻri: Toʻgʻri yoki Notoʻgʻri.
-Qisqa javob: javob(lar), bir nechta boʻlsa ; bilan ajrating (masalan: 6; olti).</t>
+Qisqa javob: javob(lar), bir nechta boʻlsa ; bilan ajrating (masalan: 6; olti).
+Moslashtirish: boʻsh qoldiring (juftliklar variantlarda).
+Koʻp bosqichli: har bir qadam uchun harf, vergul bilan (masalan: A, C, B).</t>
         </is>
       </c>
     </row>
@@ -9749,34 +9922,34 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Moslashtirish</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>2–4 juftlik, har biri alohida katakda: “Chap = Oʻng”. Oʻng tomondagi javoblar takrorlanishi mumkin. Oʻquvchiga javoblar aralashtirib koʻrsatiladi; qisman toʻgʻri moslash qisman ball oladi.</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Koʻp bosqichli</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>2–4 qadamli zanjir: har bir katak “Qadam matni || variant | variant | variant”, “Toʻgʻri javob” ustunida har bir qadam uchun harf (A, B, A). Keyingi qadam faqat oldingisi toʻgʻri boʻlsa ochiladi; toʻliq zanjir bonus ball beradi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Maslahatlar</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Toʻgʻri javoblar faqat serverda saqlanadi va oʻquvchilarga javob vaqti tugaguncha yuborilmaydi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Toʻgʻri javob har doim A boʻlib qolmasin — variantlarni aralashtiring.</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9961,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Rasmlarni kompyuterdan yuklash: importdan keyin savolni tahrirlang → “Rasm yuklash”.</t>
+          <t>Toʻgʻri javoblar faqat serverda saqlanadi va oʻquvchilarga javob vaqti tugaguncha yuborilmaydi.</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9973,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Bir xil savolni ikki marta yuklamaslik uchun import oynasi takroriy savollarni belgilaydi.</t>
+          <t>Toʻgʻri javob har doim A boʻlib qolmasin — variantlarni aralashtiring.</t>
         </is>
       </c>
     </row>
@@ -9811,6 +9984,30 @@
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Rasmlarni kompyuterdan yuklash: importdan keyin savolni tahrirlang → “Rasm yuklash”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Bir xil savolni ikki marta yuklamaslik uchun import oynasi takroriy savollarni belgilaydi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Eski .xls emas, .xlsx formatidan foydalaning. CSV (UTF-8) ham qabul qilinadi.</t>
         </is>
